--- a/DEVELOPMENT_ALL_OLD_NEW/ZARA/ZR.0929 - COLOR RANGE OPT3.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/ZARA/ZR.0929 - COLOR RANGE OPT3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\New Recipe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\ZARA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E49097-2B04-4841-90C1-79AF026D8BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9868BD-E55F-49FE-8645-5997EE6FF473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{03F72CB8-A56F-4518-8414-4CE548D4EDEC}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="mühendisler">[1]Sayfa6!$A$2:$A$10</definedName>
     <definedName name="Müşteriler">[1]Sayfa6!$B$2:$B$20</definedName>
     <definedName name="NEW">[2]DATA!$C$2:$C$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$81</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">SABLON!$A$1:$K$91</definedName>
     <definedName name="SUPERVISOR">[2]DATA!$B$2:$B$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="68">
   <si>
     <t>dcr</t>
   </si>
@@ -212,9 +212,6 @@
     <t xml:space="preserve">EXTRACT &amp; DRYER </t>
   </si>
   <si>
-    <t>NOTE !!!</t>
-  </si>
-  <si>
     <t>HYPO/BLEACH</t>
   </si>
   <si>
@@ -233,7 +230,34 @@
     <t>ROYACTIVEX KS</t>
   </si>
   <si>
-    <t>DECREASE HYPO 1 LEVEL</t>
+    <t>WHISKER</t>
+  </si>
+  <si>
+    <t>HAND SAND (400)</t>
+  </si>
+  <si>
+    <t>TAGGING (12)</t>
+  </si>
+  <si>
+    <t>HYPO/PP SPRAY</t>
+  </si>
+  <si>
+    <t>GR/LT</t>
+  </si>
+  <si>
+    <t>PERMENGANATE</t>
+  </si>
+  <si>
+    <t>ACTIVITOR</t>
+  </si>
+  <si>
+    <t>WATER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PP SPRAY </t>
+  </si>
+  <si>
+    <t>REMOVE TAGGING AFTER 10 MIN FROM ENZYME</t>
   </si>
 </sst>
 </file>
@@ -244,7 +268,7 @@
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0.0000_);_(&quot;$&quot;* \(#,##0.0000\);_(&quot;$&quot;* &quot;-&quot;????_);_(@_)"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,8 +659,16 @@
       <charset val="162"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,8 +705,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="79">
+  <borders count="81">
     <border>
       <left/>
       <right/>
@@ -1636,6 +1674,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1644,7 +1710,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2022,12 +2088,6 @@
     <xf numFmtId="164" fontId="20" fillId="5" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="5" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="53" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2121,6 +2181,90 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="80" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="80" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="80" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="79" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="80" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="79" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="80" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="80" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="80" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="79" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="7" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="7" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="79" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="79" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="47" fillId="5" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2165,6 +2309,132 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="74" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2176,126 +2446,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3149,7 +3299,7 @@
   <sheetPr codeName="Sayfa3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q111"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="5" customWidth="1"/>
@@ -3944,21 +4094,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="185">
+      <c r="C2" s="208">
         <v>46308</v>
       </c>
-      <c r="D2" s="186"/>
-      <c r="E2" s="187"/>
-      <c r="F2" s="185" t="s">
+      <c r="D2" s="209"/>
+      <c r="E2" s="210"/>
+      <c r="F2" s="208" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="186"/>
-      <c r="H2" s="188" t="s">
+      <c r="G2" s="209"/>
+      <c r="H2" s="211" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
-      <c r="K2" s="190"/>
+      <c r="I2" s="212"/>
+      <c r="J2" s="212"/>
+      <c r="K2" s="213"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3967,17 +4117,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="185" t="s">
+      <c r="C3" s="208" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="186"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="191"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="197" t="s">
+      <c r="D3" s="209"/>
+      <c r="E3" s="210"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="220" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="198"/>
+      <c r="I3" s="221"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3991,17 +4141,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="199" t="s">
+      <c r="C4" s="222" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="200"/>
-      <c r="E4" s="201"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="194"/>
-      <c r="H4" s="202"/>
-      <c r="I4" s="203"/>
-      <c r="J4" s="202"/>
-      <c r="K4" s="203"/>
+      <c r="D4" s="223"/>
+      <c r="E4" s="224"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="217"/>
+      <c r="H4" s="225"/>
+      <c r="I4" s="226"/>
+      <c r="J4" s="225"/>
+      <c r="K4" s="226"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -4010,17 +4160,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="204" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="205"/>
-      <c r="E5" s="206"/>
-      <c r="F5" s="193"/>
-      <c r="G5" s="194"/>
-      <c r="H5" s="183"/>
-      <c r="I5" s="184"/>
-      <c r="J5" s="183"/>
-      <c r="K5" s="184"/>
+      <c r="C5" s="227">
+        <v>6001383</v>
+      </c>
+      <c r="D5" s="228"/>
+      <c r="E5" s="229"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="230"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="231"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -4029,17 +4179,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="207" t="s">
+      <c r="C6" s="232" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="208"/>
-      <c r="E6" s="209"/>
-      <c r="F6" s="193"/>
-      <c r="G6" s="194"/>
-      <c r="H6" s="183"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="183"/>
-      <c r="K6" s="184"/>
+      <c r="D6" s="233"/>
+      <c r="E6" s="234"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="230"/>
+      <c r="I6" s="231"/>
+      <c r="J6" s="230"/>
+      <c r="K6" s="231"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -4048,17 +4198,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="180" t="s">
+      <c r="C7" s="241" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="181"/>
-      <c r="E7" s="182"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="194"/>
-      <c r="H7" s="183"/>
-      <c r="I7" s="184"/>
-      <c r="J7" s="183"/>
-      <c r="K7" s="184"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="230"/>
+      <c r="I7" s="231"/>
+      <c r="J7" s="230"/>
+      <c r="K7" s="231"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -4067,17 +4217,17 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="210" t="s">
+      <c r="C8" s="235" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="211"/>
-      <c r="E8" s="212"/>
-      <c r="F8" s="193"/>
-      <c r="G8" s="194"/>
+      <c r="D8" s="236"/>
+      <c r="E8" s="237"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="217"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="183"/>
-      <c r="K8" s="184"/>
+      <c r="J8" s="230"/>
+      <c r="K8" s="231"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -4086,17 +4236,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="213">
+      <c r="C9" s="238">
         <v>1</v>
       </c>
-      <c r="D9" s="214"/>
-      <c r="E9" s="215"/>
-      <c r="F9" s="193"/>
-      <c r="G9" s="194"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="217"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="183"/>
-      <c r="K9" s="184"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="231"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -4105,15 +4255,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="213"/>
-      <c r="D10" s="214"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="193"/>
-      <c r="G10" s="194"/>
+      <c r="C10" s="238"/>
+      <c r="D10" s="239"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="217"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="183"/>
-      <c r="K10" s="184"/>
+      <c r="J10" s="230"/>
+      <c r="K10" s="231"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -4122,15 +4272,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="216"/>
-      <c r="D11" s="217"/>
-      <c r="E11" s="218"/>
-      <c r="F11" s="193"/>
-      <c r="G11" s="194"/>
-      <c r="H11" s="183"/>
-      <c r="I11" s="184"/>
-      <c r="J11" s="183"/>
-      <c r="K11" s="184"/>
+      <c r="C11" s="244"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="217"/>
+      <c r="H11" s="230"/>
+      <c r="I11" s="231"/>
+      <c r="J11" s="230"/>
+      <c r="K11" s="231"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -4139,17 +4289,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="219" t="s">
+      <c r="C12" s="247" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="220"/>
-      <c r="E12" s="221"/>
-      <c r="F12" s="193"/>
-      <c r="G12" s="194"/>
-      <c r="H12" s="183"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="183"/>
-      <c r="K12" s="184"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="249"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="217"/>
+      <c r="H12" s="230"/>
+      <c r="I12" s="231"/>
+      <c r="J12" s="230"/>
+      <c r="K12" s="231"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -4158,15 +4308,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="216"/>
-      <c r="D13" s="217"/>
-      <c r="E13" s="218"/>
-      <c r="F13" s="195"/>
-      <c r="G13" s="196"/>
-      <c r="H13" s="183"/>
-      <c r="I13" s="184"/>
-      <c r="J13" s="183"/>
-      <c r="K13" s="184"/>
+      <c r="C13" s="244"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="218"/>
+      <c r="G13" s="219"/>
+      <c r="H13" s="230"/>
+      <c r="I13" s="231"/>
+      <c r="J13" s="230"/>
+      <c r="K13" s="231"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -4175,17 +4325,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="222"/>
-      <c r="D14" s="222"/>
-      <c r="E14" s="223"/>
-      <c r="F14" s="224" t="s">
+      <c r="C14" s="250"/>
+      <c r="D14" s="250"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="252" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="225"/>
-      <c r="H14" s="228" t="s">
+      <c r="G14" s="253"/>
+      <c r="H14" s="256" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="229"/>
+      <c r="I14" s="257"/>
       <c r="J14" s="17"/>
       <c r="K14" s="18"/>
       <c r="L14" s="4"/>
@@ -4203,14 +4353,14 @@
       <c r="E15" s="16">
         <v>1</v>
       </c>
-      <c r="F15" s="226"/>
-      <c r="G15" s="227"/>
-      <c r="H15" s="226"/>
-      <c r="I15" s="230"/>
-      <c r="J15" s="231" t="s">
+      <c r="F15" s="254"/>
+      <c r="G15" s="255"/>
+      <c r="H15" s="254"/>
+      <c r="I15" s="258"/>
+      <c r="J15" s="259" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="233" t="s">
+      <c r="K15" s="261" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -4236,288 +4386,270 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="235" t="s">
+      <c r="H16" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="235"/>
-      <c r="J16" s="232"/>
-      <c r="K16" s="234"/>
+      <c r="I16" s="263"/>
+      <c r="J16" s="260"/>
+      <c r="K16" s="262"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" spans="1:13" ht="98.1" customHeight="1">
+    <row r="17" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A17" s="26"/>
-      <c r="B17" s="116"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
-      <c r="F17" s="118"/>
-      <c r="G17" s="119"/>
-      <c r="H17" s="120"/>
-      <c r="I17" s="120"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="121"/>
+      <c r="B17" s="163" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
       <c r="L17" s="25"/>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" spans="1:13" ht="98.1" customHeight="1">
+    <row r="18" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A18" s="26"/>
-      <c r="B18" s="122" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="123">
-        <v>10</v>
-      </c>
-      <c r="D18" s="123">
-        <v>45</v>
-      </c>
-      <c r="E18" s="123">
-        <v>50</v>
-      </c>
-      <c r="F18" s="123">
-        <v>1</v>
-      </c>
-      <c r="G18" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="236" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="237"/>
-      <c r="J18" s="127"/>
-      <c r="K18" s="128"/>
+      <c r="B18" s="163" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
       <c r="L18" s="25"/>
       <c r="M18" s="25"/>
     </row>
     <row r="19" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A19" s="26"/>
-      <c r="B19" s="122"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123">
-        <v>1</v>
-      </c>
-      <c r="G19" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="125" t="s">
-        <v>37</v>
-      </c>
-      <c r="I19" s="126"/>
-      <c r="J19" s="127"/>
-      <c r="K19" s="128"/>
+      <c r="B19" s="163" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
       <c r="L19" s="25"/>
       <c r="M19" s="25"/>
     </row>
-    <row r="20" spans="1:13" ht="74.099999999999994" customHeight="1">
+    <row r="20" spans="1:13" ht="97.8" customHeight="1">
       <c r="A20" s="26"/>
-      <c r="B20" s="129" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="130">
-        <v>1</v>
-      </c>
-      <c r="D20" s="130" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="123"/>
-      <c r="F20" s="123">
-        <v>1</v>
-      </c>
-      <c r="G20" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="236" t="s">
-        <v>40</v>
-      </c>
-      <c r="I20" s="237"/>
-      <c r="J20" s="127"/>
-      <c r="K20" s="128"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="118"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="120"/>
+      <c r="I20" s="120"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="121"/>
       <c r="L20" s="25"/>
       <c r="M20" s="25"/>
     </row>
-    <row r="21" spans="1:13" ht="74.099999999999994" customHeight="1">
+    <row r="21" spans="1:13" ht="98.1" customHeight="1">
       <c r="A21" s="26"/>
-      <c r="B21" s="131"/>
-      <c r="C21" s="132"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="238"/>
-      <c r="I21" s="238"/>
-      <c r="J21" s="134"/>
-      <c r="K21" s="134"/>
+      <c r="B21" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="123">
+        <v>10</v>
+      </c>
+      <c r="D21" s="123">
+        <v>45</v>
+      </c>
+      <c r="E21" s="123">
+        <v>50</v>
+      </c>
+      <c r="F21" s="123">
+        <v>1</v>
+      </c>
+      <c r="G21" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" s="264" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="265"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="128"/>
       <c r="L21" s="25"/>
       <c r="M21" s="25"/>
     </row>
     <row r="22" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A22" s="26"/>
-      <c r="B22" s="135" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="124">
-        <v>40</v>
-      </c>
-      <c r="D22" s="124" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="124"/>
-      <c r="F22" s="136">
-        <v>40</v>
-      </c>
-      <c r="G22" s="136" t="s">
+      <c r="B22" s="122"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="123"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123">
+        <v>1</v>
+      </c>
+      <c r="G22" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="239" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="239"/>
-      <c r="J22" s="136"/>
-      <c r="K22" s="136"/>
+      <c r="H22" s="125" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="126"/>
+      <c r="J22" s="127"/>
+      <c r="K22" s="128"/>
       <c r="L22" s="25"/>
       <c r="M22" s="25"/>
     </row>
     <row r="23" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A23" s="26"/>
-      <c r="B23" s="137" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="124"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="124"/>
-      <c r="F23" s="136">
-        <v>900</v>
-      </c>
-      <c r="G23" s="136" t="s">
+      <c r="B23" s="129" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="130">
+        <v>1</v>
+      </c>
+      <c r="D23" s="130" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="123"/>
+      <c r="F23" s="123">
+        <v>1</v>
+      </c>
+      <c r="G23" s="124" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="239" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="239"/>
-      <c r="J23" s="136"/>
-      <c r="K23" s="136"/>
+      <c r="H23" s="264" t="s">
+        <v>40</v>
+      </c>
+      <c r="I23" s="265"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="128"/>
       <c r="L23" s="25"/>
       <c r="M23" s="25"/>
     </row>
     <row r="24" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A24" s="26"/>
-      <c r="B24" s="137"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="124"/>
-      <c r="E24" s="124"/>
-      <c r="F24" s="136">
-        <v>100</v>
-      </c>
-      <c r="G24" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" s="236" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="237"/>
-      <c r="J24" s="136"/>
-      <c r="K24" s="136"/>
+      <c r="B24" s="131"/>
+      <c r="C24" s="184" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="185"/>
+      <c r="E24" s="185"/>
+      <c r="F24" s="185"/>
+      <c r="G24" s="186"/>
+      <c r="H24" s="266"/>
+      <c r="I24" s="266"/>
+      <c r="J24" s="132"/>
+      <c r="K24" s="132"/>
       <c r="L24" s="25"/>
       <c r="M24" s="25"/>
     </row>
     <row r="25" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A25" s="26"/>
-      <c r="B25" s="137" t="s">
-        <v>46</v>
+      <c r="B25" s="133" t="s">
+        <v>41</v>
       </c>
       <c r="C25" s="124">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D25" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="138"/>
-      <c r="F25" s="139">
-        <v>10</v>
-      </c>
-      <c r="G25" s="140" t="s">
-        <v>47</v>
-      </c>
-      <c r="H25" s="246" t="s">
-        <v>48</v>
-      </c>
-      <c r="I25" s="246"/>
-      <c r="J25" s="136"/>
-      <c r="K25" s="136"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="134">
+        <v>40</v>
+      </c>
+      <c r="G25" s="134" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" s="267" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="267"/>
+      <c r="J25" s="134"/>
+      <c r="K25" s="134"/>
       <c r="L25" s="25"/>
       <c r="M25" s="25"/>
     </row>
     <row r="26" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A26" s="26"/>
-      <c r="B26" s="116"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="118"/>
+      <c r="B26" s="135" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="134">
+        <v>900</v>
+      </c>
+      <c r="G26" s="134" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="267" t="s">
+        <v>44</v>
+      </c>
+      <c r="I26" s="267"/>
+      <c r="J26" s="134"/>
+      <c r="K26" s="134"/>
       <c r="L26" s="25"/>
       <c r="M26" s="25"/>
     </row>
     <row r="27" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A27" s="26"/>
-      <c r="B27" s="122" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="159">
-        <v>8</v>
-      </c>
-      <c r="D27" s="159" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="159">
-        <v>50</v>
-      </c>
-      <c r="F27" s="160">
-        <v>4</v>
-      </c>
-      <c r="G27" s="161" t="s">
-        <v>47</v>
-      </c>
-      <c r="H27" s="174" t="s">
-        <v>54</v>
-      </c>
-      <c r="I27" s="175"/>
-      <c r="J27" s="160"/>
-      <c r="K27" s="160"/>
+      <c r="B27" s="135"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="134">
+        <v>100</v>
+      </c>
+      <c r="G27" s="124" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" s="264" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" s="265"/>
+      <c r="J27" s="134"/>
+      <c r="K27" s="134"/>
       <c r="L27" s="25"/>
       <c r="M27" s="25"/>
     </row>
     <row r="28" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A28" s="26"/>
-      <c r="B28" s="162" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="163">
-        <v>2</v>
-      </c>
-      <c r="D28" s="163" t="s">
+      <c r="B28" s="135" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="124">
+        <v>3</v>
+      </c>
+      <c r="D28" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="163"/>
-      <c r="F28" s="160">
-        <v>1</v>
-      </c>
-      <c r="G28" s="161" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" s="174" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="175"/>
-      <c r="J28" s="160"/>
-      <c r="K28" s="160"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="137">
+        <v>10</v>
+      </c>
+      <c r="G28" s="138" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="274" t="s">
+        <v>48</v>
+      </c>
+      <c r="I28" s="274"/>
+      <c r="J28" s="134"/>
+      <c r="K28" s="134"/>
       <c r="L28" s="25"/>
       <c r="M28" s="25"/>
     </row>
@@ -4538,744 +4670,808 @@
     </row>
     <row r="30" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A30" s="26"/>
-      <c r="B30" s="135" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="123">
+      <c r="B30" s="122" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="157">
+        <v>8</v>
+      </c>
+      <c r="D30" s="157" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="157">
+        <v>50</v>
+      </c>
+      <c r="F30" s="158">
         <v>3</v>
       </c>
-      <c r="D30" s="123" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="123">
-        <v>50</v>
-      </c>
-      <c r="F30" s="164">
-        <v>1</v>
-      </c>
-      <c r="G30" s="148" t="s">
-        <v>35</v>
-      </c>
-      <c r="H30" s="176" t="s">
-        <v>58</v>
-      </c>
-      <c r="I30" s="177"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="128"/>
+      <c r="G30" s="159" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="200" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="201"/>
+      <c r="J30" s="158"/>
+      <c r="K30" s="158"/>
       <c r="L30" s="25"/>
       <c r="M30" s="25"/>
     </row>
     <row r="31" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A31" s="26"/>
-      <c r="B31" s="135" t="s">
+      <c r="B31" s="160" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="161">
+        <v>2</v>
+      </c>
+      <c r="D31" s="161" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="161"/>
+      <c r="F31" s="158">
+        <v>1</v>
+      </c>
+      <c r="G31" s="159" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31" s="200" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="123">
-        <v>2</v>
-      </c>
-      <c r="D31" s="123" t="s">
-        <v>39</v>
-      </c>
-      <c r="E31" s="123"/>
-      <c r="F31" s="128"/>
-      <c r="G31" s="128"/>
-      <c r="H31" s="178"/>
-      <c r="I31" s="179"/>
-      <c r="J31" s="128"/>
-      <c r="K31" s="128"/>
+      <c r="I31" s="201"/>
+      <c r="J31" s="158"/>
+      <c r="K31" s="158"/>
       <c r="L31" s="25"/>
       <c r="M31" s="25"/>
     </row>
     <row r="32" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A32" s="26"/>
-      <c r="B32" s="141"/>
-      <c r="C32" s="142"/>
-      <c r="D32" s="165"/>
-      <c r="E32" s="165"/>
-      <c r="F32" s="143"/>
-      <c r="G32" s="143"/>
-      <c r="H32" s="241"/>
-      <c r="I32" s="241"/>
-      <c r="J32" s="143"/>
-      <c r="K32" s="143"/>
+      <c r="B32" s="116"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
+      <c r="G32" s="118"/>
+      <c r="H32" s="116"/>
+      <c r="I32" s="116"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="118"/>
       <c r="L32" s="25"/>
       <c r="M32" s="25"/>
     </row>
     <row r="33" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A33" s="26"/>
-      <c r="B33" s="144" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="145">
-        <v>2</v>
-      </c>
-      <c r="D33" s="146" t="s">
+      <c r="B33" s="133" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="123">
+        <v>3</v>
+      </c>
+      <c r="D33" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="E33" s="146">
+      <c r="E33" s="123">
         <v>50</v>
       </c>
-      <c r="F33" s="147">
+      <c r="F33" s="162">
         <v>1</v>
       </c>
-      <c r="G33" s="148" t="s">
-        <v>47</v>
-      </c>
-      <c r="H33" s="166" t="s">
-        <v>50</v>
-      </c>
-      <c r="I33" s="166"/>
-      <c r="J33" s="136"/>
-      <c r="K33" s="149"/>
+      <c r="G33" s="146" t="s">
+        <v>35</v>
+      </c>
+      <c r="H33" s="202" t="s">
+        <v>57</v>
+      </c>
+      <c r="I33" s="203"/>
+      <c r="J33" s="128"/>
+      <c r="K33" s="128"/>
       <c r="L33" s="25"/>
       <c r="M33" s="25"/>
     </row>
     <row r="34" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A34" s="26"/>
-      <c r="B34" s="137" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="136"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="167"/>
-      <c r="I34" s="167"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="136"/>
+      <c r="B34" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="C34" s="123">
+        <v>2</v>
+      </c>
+      <c r="D34" s="123" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="123"/>
+      <c r="F34" s="128"/>
+      <c r="G34" s="128"/>
+      <c r="H34" s="204"/>
+      <c r="I34" s="205"/>
+      <c r="J34" s="128"/>
+      <c r="K34" s="128"/>
       <c r="L34" s="25"/>
       <c r="M34" s="25"/>
     </row>
     <row r="35" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A35" s="26"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="150"/>
-      <c r="D35" s="150"/>
-      <c r="E35" s="150"/>
-      <c r="F35" s="150"/>
-      <c r="G35" s="151"/>
-      <c r="H35" s="242"/>
-      <c r="I35" s="243"/>
-      <c r="J35" s="154"/>
-      <c r="K35" s="29"/>
+      <c r="B35" s="167"/>
+      <c r="C35" s="187" t="s">
+        <v>66</v>
+      </c>
+      <c r="D35" s="188"/>
+      <c r="E35" s="188"/>
+      <c r="F35" s="188"/>
+      <c r="G35" s="189"/>
+      <c r="H35" s="168"/>
+      <c r="I35" s="169"/>
+      <c r="J35" s="170"/>
+      <c r="K35" s="171"/>
       <c r="L35" s="25"/>
       <c r="M35" s="25"/>
     </row>
     <row r="36" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A36" s="26"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="150"/>
-      <c r="D36" s="150"/>
-      <c r="E36" s="150"/>
-      <c r="F36" s="150"/>
-      <c r="G36" s="151"/>
-      <c r="H36" s="152"/>
-      <c r="I36" s="153"/>
-      <c r="J36" s="154"/>
-      <c r="K36" s="29"/>
+      <c r="B36" s="164" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="165"/>
+      <c r="D36" s="165"/>
+      <c r="E36" s="165"/>
+      <c r="F36" s="172">
+        <v>5</v>
+      </c>
+      <c r="G36" s="173" t="s">
+        <v>62</v>
+      </c>
+      <c r="H36" s="190" t="s">
+        <v>63</v>
+      </c>
+      <c r="I36" s="190"/>
+      <c r="J36" s="172"/>
+      <c r="K36" s="172"/>
       <c r="L36" s="25"/>
       <c r="M36" s="25"/>
     </row>
     <row r="37" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A37" s="26"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="150"/>
-      <c r="D37" s="150"/>
-      <c r="E37" s="150"/>
-      <c r="F37" s="150"/>
-      <c r="G37" s="151"/>
-      <c r="H37" s="152"/>
-      <c r="I37" s="153"/>
-      <c r="J37" s="154"/>
-      <c r="K37" s="29"/>
+      <c r="B37" s="164"/>
+      <c r="C37" s="165"/>
+      <c r="D37" s="165"/>
+      <c r="E37" s="165"/>
+      <c r="F37" s="172">
+        <v>5</v>
+      </c>
+      <c r="G37" s="173" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" s="190" t="s">
+        <v>64</v>
+      </c>
+      <c r="I37" s="190"/>
+      <c r="J37" s="172"/>
+      <c r="K37" s="172"/>
       <c r="L37" s="25"/>
       <c r="M37" s="25"/>
     </row>
     <row r="38" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A38" s="26"/>
-      <c r="B38" s="155"/>
-      <c r="C38" s="168" t="s">
-        <v>59</v>
-      </c>
-      <c r="D38" s="169"/>
-      <c r="E38" s="169"/>
-      <c r="F38" s="169"/>
-      <c r="G38" s="170"/>
-      <c r="H38" s="156"/>
-      <c r="I38" s="157"/>
-      <c r="J38" s="134"/>
-      <c r="K38" s="134"/>
+      <c r="B38" s="174"/>
+      <c r="C38" s="165"/>
+      <c r="D38" s="165"/>
+      <c r="E38" s="165"/>
+      <c r="F38" s="172">
+        <v>1</v>
+      </c>
+      <c r="G38" s="173" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" s="190" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" s="190"/>
+      <c r="J38" s="172"/>
+      <c r="K38" s="172"/>
       <c r="L38" s="25"/>
       <c r="M38" s="25"/>
     </row>
     <row r="39" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A39" s="26"/>
-      <c r="B39" s="129" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="171"/>
-      <c r="D39" s="172"/>
-      <c r="E39" s="172"/>
-      <c r="F39" s="172"/>
-      <c r="G39" s="173"/>
-      <c r="H39" s="244"/>
-      <c r="I39" s="244"/>
-      <c r="J39" s="158"/>
-      <c r="K39" s="158"/>
+      <c r="B39" s="175"/>
+      <c r="C39" s="176"/>
+      <c r="D39" s="176"/>
+      <c r="E39" s="176"/>
+      <c r="F39" s="170"/>
+      <c r="G39" s="177"/>
+      <c r="H39" s="178"/>
+      <c r="I39" s="179"/>
+      <c r="J39" s="170"/>
+      <c r="K39" s="170"/>
       <c r="L39" s="25"/>
       <c r="M39" s="25"/>
     </row>
     <row r="40" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A40" s="26"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="245"/>
-      <c r="I40" s="245"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
+      <c r="B40" s="164" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="165">
+        <v>2</v>
+      </c>
+      <c r="D40" s="165" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="165">
+        <v>50</v>
+      </c>
+      <c r="F40" s="172">
+        <v>2</v>
+      </c>
+      <c r="G40" s="173" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="206" t="s">
+        <v>57</v>
+      </c>
+      <c r="I40" s="207"/>
+      <c r="J40" s="166"/>
+      <c r="K40" s="166"/>
       <c r="L40" s="25"/>
       <c r="M40" s="25"/>
     </row>
     <row r="41" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A41" s="26"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
+      <c r="B41" s="180" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="181">
+        <v>2</v>
+      </c>
+      <c r="D41" s="182" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" s="181"/>
+      <c r="F41" s="172"/>
+      <c r="G41" s="172"/>
+      <c r="H41" s="190"/>
+      <c r="I41" s="190"/>
+      <c r="J41" s="183"/>
+      <c r="K41" s="183"/>
       <c r="L41" s="25"/>
       <c r="M41" s="25"/>
     </row>
     <row r="42" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A42" s="26"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="247"/>
-      <c r="I42" s="248"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
+      <c r="B42" s="139"/>
+      <c r="C42" s="140"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="191"/>
+      <c r="F42" s="141"/>
+      <c r="G42" s="141"/>
+      <c r="H42" s="269"/>
+      <c r="I42" s="269"/>
+      <c r="J42" s="141"/>
+      <c r="K42" s="141"/>
       <c r="L42" s="25"/>
       <c r="M42" s="25"/>
     </row>
     <row r="43" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A43" s="26"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="24"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="247"/>
-      <c r="I43" s="248"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
+      <c r="B43" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="143">
+        <v>2</v>
+      </c>
+      <c r="D43" s="144" t="s">
+        <v>39</v>
+      </c>
+      <c r="E43" s="144">
+        <v>50</v>
+      </c>
+      <c r="F43" s="145">
+        <v>1</v>
+      </c>
+      <c r="G43" s="146" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="192" t="s">
+        <v>50</v>
+      </c>
+      <c r="I43" s="192"/>
+      <c r="J43" s="134"/>
+      <c r="K43" s="147"/>
       <c r="L43" s="25"/>
       <c r="M43" s="25"/>
     </row>
     <row r="44" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A44" s="26"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="249"/>
-      <c r="I44" s="250"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="42"/>
+      <c r="B44" s="135" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="134"/>
+      <c r="D44" s="134"/>
+      <c r="E44" s="134"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="147"/>
+      <c r="H44" s="193"/>
+      <c r="I44" s="193"/>
+      <c r="J44" s="134"/>
+      <c r="K44" s="134"/>
       <c r="L44" s="25"/>
       <c r="M44" s="25"/>
     </row>
     <row r="45" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A45" s="26"/>
-      <c r="B45" s="43"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="148"/>
+      <c r="D45" s="148"/>
+      <c r="E45" s="148"/>
+      <c r="F45" s="148"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="270"/>
+      <c r="I45" s="271"/>
+      <c r="J45" s="152"/>
+      <c r="K45" s="29"/>
       <c r="L45" s="25"/>
       <c r="M45" s="25"/>
     </row>
     <row r="46" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A46" s="26"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="251"/>
-      <c r="I46" s="248"/>
-      <c r="J46" s="47"/>
-      <c r="K46" s="47"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="148"/>
+      <c r="D46" s="148"/>
+      <c r="E46" s="148"/>
+      <c r="F46" s="148"/>
+      <c r="G46" s="149"/>
+      <c r="H46" s="150"/>
+      <c r="I46" s="151"/>
+      <c r="J46" s="152"/>
+      <c r="K46" s="29"/>
       <c r="L46" s="25"/>
       <c r="M46" s="25"/>
     </row>
     <row r="47" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A47" s="26"/>
-      <c r="B47" s="48"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="251"/>
-      <c r="I47" s="248"/>
-      <c r="J47" s="47"/>
-      <c r="K47" s="47"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="148"/>
+      <c r="D47" s="148"/>
+      <c r="E47" s="148"/>
+      <c r="F47" s="148"/>
+      <c r="G47" s="149"/>
+      <c r="H47" s="150"/>
+      <c r="I47" s="151"/>
+      <c r="J47" s="152"/>
+      <c r="K47" s="29"/>
       <c r="L47" s="25"/>
       <c r="M47" s="25"/>
     </row>
     <row r="48" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A48" s="26"/>
-      <c r="B48" s="43"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="46"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
+      <c r="B48" s="153"/>
+      <c r="C48" s="194"/>
+      <c r="D48" s="195"/>
+      <c r="E48" s="195"/>
+      <c r="F48" s="195"/>
+      <c r="G48" s="196"/>
+      <c r="H48" s="154"/>
+      <c r="I48" s="155"/>
+      <c r="J48" s="132"/>
+      <c r="K48" s="132"/>
       <c r="L48" s="25"/>
       <c r="M48" s="25"/>
     </row>
     <row r="49" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A49" s="26"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="52"/>
-      <c r="H49" s="240"/>
-      <c r="I49" s="240"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="42"/>
+      <c r="B49" s="129"/>
+      <c r="C49" s="197"/>
+      <c r="D49" s="198"/>
+      <c r="E49" s="198"/>
+      <c r="F49" s="198"/>
+      <c r="G49" s="199"/>
+      <c r="H49" s="272"/>
+      <c r="I49" s="272"/>
+      <c r="J49" s="156"/>
+      <c r="K49" s="156"/>
       <c r="L49" s="25"/>
       <c r="M49" s="25"/>
     </row>
     <row r="50" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A50" s="26"/>
-      <c r="B50" s="48"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="54"/>
-      <c r="H50" s="254"/>
-      <c r="I50" s="255"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="55"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="273"/>
+      <c r="I50" s="273"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="34"/>
       <c r="L50" s="25"/>
       <c r="M50" s="25"/>
     </row>
     <row r="51" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A51" s="26"/>
-      <c r="B51" s="56"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="59"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="27"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="32"/>
       <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
+      <c r="J51" s="27"/>
+      <c r="K51" s="27"/>
       <c r="L51" s="25"/>
       <c r="M51" s="25"/>
     </row>
     <row r="52" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A52" s="26"/>
-      <c r="B52" s="60"/>
-      <c r="C52" s="256"/>
-      <c r="D52" s="257"/>
-      <c r="E52" s="257"/>
-      <c r="F52" s="257"/>
-      <c r="G52" s="258"/>
-      <c r="H52" s="259"/>
-      <c r="I52" s="259"/>
-      <c r="J52" s="61"/>
-      <c r="K52" s="61"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="275"/>
+      <c r="I52" s="276"/>
+      <c r="J52" s="34"/>
+      <c r="K52" s="34"/>
       <c r="L52" s="25"/>
       <c r="M52" s="25"/>
     </row>
     <row r="53" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A53" s="26"/>
-      <c r="B53" s="62"/>
-      <c r="C53" s="63"/>
-      <c r="D53" s="63"/>
-      <c r="E53" s="63"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="64"/>
-      <c r="H53" s="260"/>
-      <c r="I53" s="260"/>
-      <c r="J53" s="61"/>
-      <c r="K53" s="61"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="275"/>
+      <c r="I53" s="276"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
       <c r="L53" s="25"/>
       <c r="M53" s="25"/>
     </row>
     <row r="54" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A54" s="26"/>
-      <c r="B54" s="65"/>
-      <c r="C54" s="66"/>
-      <c r="D54" s="66"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="64"/>
-      <c r="H54" s="260"/>
-      <c r="I54" s="260"/>
-      <c r="J54" s="61"/>
-      <c r="K54" s="61"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="39"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="277"/>
+      <c r="I54" s="278"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="42"/>
       <c r="L54" s="25"/>
       <c r="M54" s="25"/>
     </row>
     <row r="55" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A55" s="26"/>
-      <c r="B55" s="65"/>
-      <c r="C55" s="66"/>
-      <c r="D55" s="66"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="260"/>
-      <c r="I55" s="260"/>
-      <c r="J55" s="61"/>
-      <c r="K55" s="61"/>
+      <c r="B55" s="43"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="46"/>
+      <c r="I55" s="33"/>
+      <c r="J55" s="45"/>
+      <c r="K55" s="45"/>
       <c r="L55" s="25"/>
       <c r="M55" s="25"/>
     </row>
     <row r="56" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A56" s="26"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="261"/>
-      <c r="D56" s="262"/>
-      <c r="E56" s="262"/>
-      <c r="F56" s="262"/>
-      <c r="G56" s="263"/>
-      <c r="H56" s="264"/>
-      <c r="I56" s="265"/>
-      <c r="J56" s="56"/>
-      <c r="K56" s="56"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="47"/>
+      <c r="H56" s="279"/>
+      <c r="I56" s="276"/>
+      <c r="J56" s="47"/>
+      <c r="K56" s="47"/>
       <c r="L56" s="25"/>
       <c r="M56" s="25"/>
     </row>
     <row r="57" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A57" s="26"/>
-      <c r="B57" s="68"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="266"/>
-      <c r="I57" s="267"/>
-      <c r="J57" s="70"/>
-      <c r="K57" s="66"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="47"/>
+      <c r="G57" s="47"/>
+      <c r="H57" s="279"/>
+      <c r="I57" s="276"/>
+      <c r="J57" s="47"/>
+      <c r="K57" s="47"/>
       <c r="L57" s="25"/>
       <c r="M57" s="25"/>
     </row>
     <row r="58" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A58" s="26"/>
-      <c r="B58" s="68"/>
-      <c r="C58" s="66"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="69"/>
-      <c r="G58" s="69"/>
-      <c r="H58" s="266"/>
-      <c r="I58" s="268"/>
-      <c r="J58" s="70"/>
-      <c r="K58" s="66"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="33"/>
+      <c r="J58" s="45"/>
+      <c r="K58" s="45"/>
       <c r="L58" s="25"/>
       <c r="M58" s="25"/>
     </row>
-    <row r="59" spans="1:13" ht="71.099999999999994" customHeight="1">
+    <row r="59" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A59" s="26"/>
-      <c r="B59" s="71"/>
-      <c r="C59" s="72"/>
-      <c r="D59" s="72"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="69"/>
-      <c r="G59" s="69"/>
-      <c r="H59" s="266"/>
+      <c r="B59" s="50"/>
+      <c r="C59" s="51"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="268"/>
       <c r="I59" s="268"/>
-      <c r="J59" s="70"/>
-      <c r="K59" s="66"/>
+      <c r="J59" s="41"/>
+      <c r="K59" s="42"/>
       <c r="L59" s="25"/>
       <c r="M59" s="25"/>
     </row>
-    <row r="60" spans="1:13" ht="71.099999999999994" customHeight="1">
+    <row r="60" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A60" s="26"/>
-      <c r="B60" s="71"/>
-      <c r="C60" s="72"/>
-      <c r="D60" s="72"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="73"/>
-      <c r="H60" s="252"/>
-      <c r="I60" s="253"/>
-      <c r="J60" s="70"/>
-      <c r="K60" s="66"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="282"/>
+      <c r="I60" s="283"/>
+      <c r="J60" s="41"/>
+      <c r="K60" s="55"/>
       <c r="L60" s="25"/>
       <c r="M60" s="25"/>
     </row>
-    <row r="61" spans="1:13" ht="71.099999999999994" customHeight="1">
+    <row r="61" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A61" s="26"/>
-      <c r="B61" s="74"/>
-      <c r="C61" s="75"/>
-      <c r="D61" s="75"/>
-      <c r="E61" s="75"/>
-      <c r="F61" s="76"/>
-      <c r="G61" s="76"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
       <c r="H61" s="59"/>
       <c r="I61" s="33"/>
-      <c r="J61" s="76"/>
-      <c r="K61" s="76"/>
+      <c r="J61" s="33"/>
+      <c r="K61" s="33"/>
       <c r="L61" s="25"/>
       <c r="M61" s="25"/>
     </row>
-    <row r="62" spans="1:13" ht="71.099999999999994" customHeight="1">
+    <row r="62" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A62" s="26"/>
-      <c r="B62" s="62"/>
-      <c r="C62" s="63"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="64"/>
-      <c r="H62" s="270"/>
-      <c r="I62" s="270"/>
-      <c r="J62" s="66"/>
-      <c r="K62" s="66"/>
+      <c r="B62" s="60"/>
+      <c r="C62" s="284"/>
+      <c r="D62" s="285"/>
+      <c r="E62" s="285"/>
+      <c r="F62" s="285"/>
+      <c r="G62" s="286"/>
+      <c r="H62" s="287"/>
+      <c r="I62" s="287"/>
+      <c r="J62" s="61"/>
+      <c r="K62" s="61"/>
       <c r="L62" s="25"/>
       <c r="M62" s="25"/>
     </row>
-    <row r="63" spans="1:13" ht="77.099999999999994" customHeight="1">
+    <row r="63" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A63" s="26"/>
       <c r="B63" s="62"/>
       <c r="C63" s="63"/>
       <c r="D63" s="63"/>
       <c r="E63" s="63"/>
-      <c r="F63" s="66"/>
-      <c r="G63" s="66"/>
-      <c r="H63" s="271"/>
-      <c r="I63" s="271"/>
-      <c r="J63" s="66"/>
-      <c r="K63" s="66"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="288"/>
+      <c r="I63" s="288"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="61"/>
       <c r="L63" s="25"/>
       <c r="M63" s="25"/>
     </row>
     <row r="64" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A64" s="77"/>
-      <c r="B64" s="78"/>
-      <c r="C64" s="79"/>
-      <c r="D64" s="79"/>
-      <c r="E64" s="79"/>
-      <c r="F64" s="80"/>
-      <c r="G64" s="81"/>
-      <c r="H64" s="82"/>
-      <c r="I64" s="83"/>
-      <c r="J64" s="84"/>
-      <c r="K64" s="84"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="85"/>
+      <c r="A64" s="26"/>
+      <c r="B64" s="65"/>
+      <c r="C64" s="66"/>
+      <c r="D64" s="66"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="61"/>
+      <c r="G64" s="64"/>
+      <c r="H64" s="288"/>
+      <c r="I64" s="288"/>
+      <c r="J64" s="61"/>
+      <c r="K64" s="61"/>
+      <c r="L64" s="25"/>
+      <c r="M64" s="25"/>
     </row>
     <row r="65" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A65" s="77"/>
-      <c r="B65" s="62"/>
-      <c r="C65" s="63"/>
-      <c r="D65" s="63"/>
+      <c r="A65" s="26"/>
+      <c r="B65" s="65"/>
+      <c r="C65" s="66"/>
+      <c r="D65" s="66"/>
       <c r="E65" s="63"/>
       <c r="F65" s="61"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="260"/>
-      <c r="I65" s="260"/>
+      <c r="G65" s="64"/>
+      <c r="H65" s="288"/>
+      <c r="I65" s="288"/>
       <c r="J65" s="61"/>
       <c r="K65" s="61"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="85"/>
+      <c r="L65" s="25"/>
+      <c r="M65" s="25"/>
     </row>
     <row r="66" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A66" s="77"/>
-      <c r="B66" s="62"/>
-      <c r="C66" s="63"/>
-      <c r="D66" s="63"/>
-      <c r="E66" s="63"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="260"/>
-      <c r="I66" s="260"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="61"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="85"/>
+      <c r="A66" s="26"/>
+      <c r="B66" s="67"/>
+      <c r="C66" s="289"/>
+      <c r="D66" s="290"/>
+      <c r="E66" s="290"/>
+      <c r="F66" s="290"/>
+      <c r="G66" s="291"/>
+      <c r="H66" s="292"/>
+      <c r="I66" s="293"/>
+      <c r="J66" s="56"/>
+      <c r="K66" s="56"/>
+      <c r="L66" s="25"/>
+      <c r="M66" s="25"/>
     </row>
     <row r="67" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A67" s="77"/>
-      <c r="B67" s="86"/>
-      <c r="C67" s="75"/>
-      <c r="D67" s="75"/>
-      <c r="E67" s="75"/>
-      <c r="F67" s="76"/>
-      <c r="G67" s="76"/>
-      <c r="H67" s="272"/>
-      <c r="I67" s="273"/>
-      <c r="J67" s="76"/>
-      <c r="K67" s="87"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="85"/>
+      <c r="A67" s="26"/>
+      <c r="B67" s="68"/>
+      <c r="C67" s="66"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="69"/>
+      <c r="G67" s="69"/>
+      <c r="H67" s="294"/>
+      <c r="I67" s="295"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="66"/>
+      <c r="L67" s="25"/>
+      <c r="M67" s="25"/>
     </row>
     <row r="68" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A68" s="77"/>
-      <c r="B68" s="88"/>
-      <c r="C68" s="89"/>
-      <c r="D68" s="89"/>
-      <c r="E68" s="89"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="73"/>
-      <c r="H68" s="274"/>
-      <c r="I68" s="274"/>
-      <c r="J68" s="73"/>
-      <c r="K68" s="73"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="85"/>
-    </row>
-    <row r="69" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A69" s="77"/>
-      <c r="B69" s="90"/>
-      <c r="C69" s="89"/>
-      <c r="D69" s="89"/>
-      <c r="E69" s="89"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="275"/>
-      <c r="I69" s="275"/>
-      <c r="J69" s="73"/>
-      <c r="K69" s="73"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="85"/>
-    </row>
-    <row r="70" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A70" s="77"/>
-      <c r="B70" s="62"/>
-      <c r="C70" s="63"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="63"/>
+      <c r="A68" s="26"/>
+      <c r="B68" s="68"/>
+      <c r="C68" s="66"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="69"/>
+      <c r="G68" s="69"/>
+      <c r="H68" s="294"/>
+      <c r="I68" s="296"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="66"/>
+      <c r="L68" s="25"/>
+      <c r="M68" s="25"/>
+    </row>
+    <row r="69" spans="1:13" ht="71.099999999999994" customHeight="1">
+      <c r="A69" s="26"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="72"/>
+      <c r="D69" s="72"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="69"/>
+      <c r="G69" s="69"/>
+      <c r="H69" s="294"/>
+      <c r="I69" s="296"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="66"/>
+      <c r="L69" s="25"/>
+      <c r="M69" s="25"/>
+    </row>
+    <row r="70" spans="1:13" ht="71.099999999999994" customHeight="1">
+      <c r="A70" s="26"/>
+      <c r="B70" s="71"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="72"/>
+      <c r="E70" s="66"/>
       <c r="F70" s="66"/>
-      <c r="G70" s="66"/>
-      <c r="H70" s="276"/>
-      <c r="I70" s="276"/>
-      <c r="J70" s="66"/>
+      <c r="G70" s="73"/>
+      <c r="H70" s="280"/>
+      <c r="I70" s="281"/>
+      <c r="J70" s="70"/>
       <c r="K70" s="66"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="85"/>
-    </row>
-    <row r="71" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A71" s="77"/>
-      <c r="B71" s="86"/>
-      <c r="C71" s="91"/>
-      <c r="D71" s="91"/>
-      <c r="E71" s="91"/>
+      <c r="L70" s="25"/>
+      <c r="M70" s="25"/>
+    </row>
+    <row r="71" spans="1:13" ht="71.099999999999994" customHeight="1">
+      <c r="A71" s="26"/>
+      <c r="B71" s="74"/>
+      <c r="C71" s="75"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
       <c r="F71" s="76"/>
       <c r="G71" s="76"/>
       <c r="H71" s="59"/>
-      <c r="I71" s="92"/>
+      <c r="I71" s="33"/>
       <c r="J71" s="76"/>
       <c r="K71" s="76"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="85"/>
-    </row>
-    <row r="72" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A72" s="77"/>
+      <c r="L71" s="25"/>
+      <c r="M71" s="25"/>
+    </row>
+    <row r="72" spans="1:13" ht="71.099999999999994" customHeight="1">
+      <c r="A72" s="26"/>
       <c r="B72" s="62"/>
       <c r="C72" s="63"/>
       <c r="D72" s="63"/>
       <c r="E72" s="63"/>
-      <c r="F72" s="66"/>
-      <c r="G72" s="66"/>
-      <c r="H72" s="277"/>
-      <c r="I72" s="278"/>
+      <c r="F72" s="61"/>
+      <c r="G72" s="64"/>
+      <c r="H72" s="298"/>
+      <c r="I72" s="298"/>
       <c r="J72" s="66"/>
       <c r="K72" s="66"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="85"/>
-    </row>
-    <row r="73" spans="1:13" ht="74.099999999999994" customHeight="1">
-      <c r="A73" s="77"/>
+      <c r="L72" s="25"/>
+      <c r="M72" s="25"/>
+    </row>
+    <row r="73" spans="1:13" ht="77.099999999999994" customHeight="1">
+      <c r="A73" s="26"/>
       <c r="B73" s="62"/>
       <c r="C73" s="63"/>
       <c r="D73" s="63"/>
       <c r="E73" s="63"/>
       <c r="F73" s="66"/>
       <c r="G73" s="66"/>
-      <c r="H73" s="277"/>
-      <c r="I73" s="278"/>
+      <c r="H73" s="299"/>
+      <c r="I73" s="299"/>
       <c r="J73" s="66"/>
       <c r="K73" s="66"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="85"/>
+      <c r="L73" s="25"/>
+      <c r="M73" s="25"/>
     </row>
     <row r="74" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A74" s="77"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="93"/>
-      <c r="D74" s="93"/>
-      <c r="E74" s="93"/>
-      <c r="F74" s="93"/>
-      <c r="G74" s="93"/>
-      <c r="H74" s="59"/>
-      <c r="I74" s="92"/>
-      <c r="J74" s="76"/>
-      <c r="K74" s="76"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="79"/>
+      <c r="D74" s="79"/>
+      <c r="E74" s="79"/>
+      <c r="F74" s="80"/>
+      <c r="G74" s="81"/>
+      <c r="H74" s="82"/>
+      <c r="I74" s="83"/>
+      <c r="J74" s="84"/>
+      <c r="K74" s="84"/>
       <c r="L74" s="4"/>
       <c r="M74" s="85"/>
     </row>
     <row r="75" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A75" s="77"/>
-      <c r="B75" s="94"/>
-      <c r="C75" s="95"/>
-      <c r="D75" s="96"/>
-      <c r="E75" s="96"/>
-      <c r="F75" s="97"/>
-      <c r="G75" s="64"/>
-      <c r="H75" s="279"/>
-      <c r="I75" s="279"/>
+      <c r="B75" s="62"/>
+      <c r="C75" s="63"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="63"/>
+      <c r="F75" s="61"/>
+      <c r="G75" s="61"/>
+      <c r="H75" s="288"/>
+      <c r="I75" s="288"/>
       <c r="J75" s="61"/>
-      <c r="K75" s="73"/>
+      <c r="K75" s="61"/>
       <c r="L75" s="4"/>
       <c r="M75" s="85"/>
     </row>
     <row r="76" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A76" s="77"/>
-      <c r="B76" s="94"/>
-      <c r="C76" s="98"/>
-      <c r="D76" s="98"/>
-      <c r="E76" s="99"/>
-      <c r="F76" s="100"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="269"/>
-      <c r="I76" s="269"/>
+      <c r="B76" s="62"/>
+      <c r="C76" s="63"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="63"/>
+      <c r="F76" s="61"/>
+      <c r="G76" s="61"/>
+      <c r="H76" s="288"/>
+      <c r="I76" s="288"/>
       <c r="J76" s="61"/>
       <c r="K76" s="61"/>
       <c r="L76" s="4"/>
@@ -5283,168 +5479,288 @@
     </row>
     <row r="77" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A77" s="77"/>
-      <c r="B77" s="101"/>
-      <c r="C77" s="102"/>
-      <c r="D77" s="102"/>
-      <c r="E77" s="102"/>
-      <c r="F77" s="103"/>
-      <c r="G77" s="103"/>
-      <c r="H77" s="282"/>
-      <c r="I77" s="282"/>
-      <c r="J77" s="104"/>
-      <c r="K77" s="104"/>
+      <c r="B77" s="86"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="76"/>
+      <c r="G77" s="76"/>
+      <c r="H77" s="300"/>
+      <c r="I77" s="301"/>
+      <c r="J77" s="76"/>
+      <c r="K77" s="87"/>
       <c r="L77" s="4"/>
       <c r="M77" s="85"/>
     </row>
     <row r="78" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A78" s="77"/>
-      <c r="B78" s="105"/>
-      <c r="C78" s="106"/>
-      <c r="D78" s="106"/>
-      <c r="E78" s="106"/>
-      <c r="F78" s="106"/>
-      <c r="G78" s="106"/>
-      <c r="H78" s="283"/>
-      <c r="I78" s="284"/>
-      <c r="J78" s="107"/>
-      <c r="K78" s="106"/>
+      <c r="B78" s="88"/>
+      <c r="C78" s="89"/>
+      <c r="D78" s="89"/>
+      <c r="E78" s="89"/>
+      <c r="F78" s="73"/>
+      <c r="G78" s="73"/>
+      <c r="H78" s="302"/>
+      <c r="I78" s="302"/>
+      <c r="J78" s="73"/>
+      <c r="K78" s="73"/>
       <c r="L78" s="4"/>
       <c r="M78" s="85"/>
     </row>
     <row r="79" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A79" s="77"/>
-      <c r="B79" s="108"/>
-      <c r="C79" s="55"/>
-      <c r="D79" s="55"/>
-      <c r="E79" s="55"/>
-      <c r="F79" s="55"/>
-      <c r="G79" s="55"/>
-      <c r="H79" s="280"/>
-      <c r="I79" s="281"/>
-      <c r="J79" s="109"/>
-      <c r="K79" s="55"/>
+      <c r="B79" s="90"/>
+      <c r="C79" s="89"/>
+      <c r="D79" s="89"/>
+      <c r="E79" s="89"/>
+      <c r="F79" s="73"/>
+      <c r="G79" s="73"/>
+      <c r="H79" s="303"/>
+      <c r="I79" s="303"/>
+      <c r="J79" s="73"/>
+      <c r="K79" s="73"/>
       <c r="L79" s="4"/>
       <c r="M79" s="85"/>
     </row>
     <row r="80" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A80" s="77"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
+      <c r="B80" s="62"/>
+      <c r="C80" s="63"/>
+      <c r="D80" s="63"/>
+      <c r="E80" s="63"/>
       <c r="F80" s="66"/>
       <c r="G80" s="66"/>
-      <c r="H80" s="285"/>
-      <c r="I80" s="285"/>
-      <c r="J80" s="110"/>
+      <c r="H80" s="304"/>
+      <c r="I80" s="304"/>
+      <c r="J80" s="66"/>
       <c r="K80" s="66"/>
       <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
+      <c r="M80" s="85"/>
     </row>
     <row r="81" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A81" s="77"/>
-      <c r="B81" s="111"/>
-      <c r="C81" s="55"/>
-      <c r="D81" s="55"/>
-      <c r="E81" s="55"/>
-      <c r="F81" s="55"/>
-      <c r="G81" s="55"/>
-      <c r="H81" s="280"/>
-      <c r="I81" s="281"/>
-      <c r="J81" s="109"/>
-      <c r="K81" s="112"/>
+      <c r="B81" s="86"/>
+      <c r="C81" s="91"/>
+      <c r="D81" s="91"/>
+      <c r="E81" s="91"/>
+      <c r="F81" s="76"/>
+      <c r="G81" s="76"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="92"/>
+      <c r="J81" s="76"/>
+      <c r="K81" s="76"/>
       <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
-    </row>
-    <row r="82" spans="1:13" ht="61.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="113"/>
-      <c r="C82" s="55"/>
-      <c r="D82" s="55"/>
-      <c r="E82" s="55"/>
-      <c r="F82" s="55"/>
-      <c r="G82" s="55"/>
-      <c r="H82" s="280"/>
-      <c r="I82" s="281"/>
-      <c r="J82" s="109"/>
-      <c r="K82" s="112"/>
-      <c r="L82" s="114"/>
-      <c r="M82" s="115"/>
-    </row>
-    <row r="83" spans="1:13" ht="61.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="113"/>
-      <c r="C83" s="55"/>
-      <c r="D83" s="55"/>
-      <c r="E83" s="55"/>
-      <c r="F83" s="55"/>
-      <c r="G83" s="55"/>
-      <c r="H83" s="280"/>
-      <c r="I83" s="281"/>
-      <c r="J83" s="109"/>
-      <c r="K83" s="112"/>
-      <c r="L83" s="114"/>
-      <c r="M83" s="115"/>
-    </row>
-    <row r="84" spans="1:13" ht="61.2">
-      <c r="A84" s="4"/>
-      <c r="B84" s="113"/>
-      <c r="C84" s="55"/>
-      <c r="D84" s="55"/>
-      <c r="E84" s="55"/>
-      <c r="F84" s="55"/>
-      <c r="G84" s="55"/>
-      <c r="H84" s="280"/>
-      <c r="I84" s="281"/>
-      <c r="J84" s="109"/>
-      <c r="K84" s="112"/>
+      <c r="M81" s="85"/>
+    </row>
+    <row r="82" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A82" s="77"/>
+      <c r="B82" s="62"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="63"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="66"/>
+      <c r="G82" s="66"/>
+      <c r="H82" s="305"/>
+      <c r="I82" s="306"/>
+      <c r="J82" s="66"/>
+      <c r="K82" s="66"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="85"/>
+    </row>
+    <row r="83" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A83" s="77"/>
+      <c r="B83" s="62"/>
+      <c r="C83" s="63"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="66"/>
+      <c r="G83" s="66"/>
+      <c r="H83" s="305"/>
+      <c r="I83" s="306"/>
+      <c r="J83" s="66"/>
+      <c r="K83" s="66"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="85"/>
+    </row>
+    <row r="84" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A84" s="77"/>
+      <c r="B84" s="67"/>
+      <c r="C84" s="93"/>
+      <c r="D84" s="93"/>
+      <c r="E84" s="93"/>
+      <c r="F84" s="93"/>
+      <c r="G84" s="93"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="92"/>
+      <c r="J84" s="76"/>
+      <c r="K84" s="76"/>
       <c r="L84" s="4"/>
-      <c r="M84" s="4"/>
-    </row>
-    <row r="85" spans="1:13">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="4"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
+      <c r="M84" s="85"/>
+    </row>
+    <row r="85" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A85" s="77"/>
+      <c r="B85" s="94"/>
+      <c r="C85" s="95"/>
+      <c r="D85" s="96"/>
+      <c r="E85" s="96"/>
+      <c r="F85" s="97"/>
+      <c r="G85" s="64"/>
+      <c r="H85" s="307"/>
+      <c r="I85" s="307"/>
+      <c r="J85" s="61"/>
+      <c r="K85" s="73"/>
       <c r="L85" s="4"/>
-      <c r="M85" s="4"/>
-    </row>
-    <row r="86" spans="1:13">
-      <c r="A86" s="4"/>
-    </row>
-    <row r="87" spans="1:13">
-      <c r="A87" s="4"/>
-    </row>
-    <row r="88" spans="1:13">
-      <c r="A88" s="4"/>
-    </row>
-    <row r="89" spans="1:13">
-      <c r="A89" s="4"/>
-    </row>
-    <row r="90" spans="1:13">
-      <c r="A90" s="4"/>
-    </row>
-    <row r="91" spans="1:13">
-      <c r="A91" s="4"/>
-    </row>
-    <row r="92" spans="1:13">
+      <c r="M85" s="85"/>
+    </row>
+    <row r="86" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A86" s="77"/>
+      <c r="B86" s="94"/>
+      <c r="C86" s="98"/>
+      <c r="D86" s="98"/>
+      <c r="E86" s="99"/>
+      <c r="F86" s="100"/>
+      <c r="G86" s="73"/>
+      <c r="H86" s="297"/>
+      <c r="I86" s="297"/>
+      <c r="J86" s="61"/>
+      <c r="K86" s="61"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="85"/>
+    </row>
+    <row r="87" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A87" s="77"/>
+      <c r="B87" s="101"/>
+      <c r="C87" s="102"/>
+      <c r="D87" s="102"/>
+      <c r="E87" s="102"/>
+      <c r="F87" s="103"/>
+      <c r="G87" s="103"/>
+      <c r="H87" s="310"/>
+      <c r="I87" s="310"/>
+      <c r="J87" s="104"/>
+      <c r="K87" s="104"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="85"/>
+    </row>
+    <row r="88" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A88" s="77"/>
+      <c r="B88" s="105"/>
+      <c r="C88" s="106"/>
+      <c r="D88" s="106"/>
+      <c r="E88" s="106"/>
+      <c r="F88" s="106"/>
+      <c r="G88" s="106"/>
+      <c r="H88" s="311"/>
+      <c r="I88" s="312"/>
+      <c r="J88" s="107"/>
+      <c r="K88" s="106"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="85"/>
+    </row>
+    <row r="89" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A89" s="77"/>
+      <c r="B89" s="108"/>
+      <c r="C89" s="55"/>
+      <c r="D89" s="55"/>
+      <c r="E89" s="55"/>
+      <c r="F89" s="55"/>
+      <c r="G89" s="55"/>
+      <c r="H89" s="308"/>
+      <c r="I89" s="309"/>
+      <c r="J89" s="109"/>
+      <c r="K89" s="55"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="85"/>
+    </row>
+    <row r="90" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A90" s="77"/>
+      <c r="B90" s="66"/>
+      <c r="C90" s="66"/>
+      <c r="D90" s="66"/>
+      <c r="E90" s="66"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="66"/>
+      <c r="H90" s="313"/>
+      <c r="I90" s="313"/>
+      <c r="J90" s="110"/>
+      <c r="K90" s="66"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="4"/>
+    </row>
+    <row r="91" spans="1:13" ht="74.099999999999994" customHeight="1">
+      <c r="A91" s="77"/>
+      <c r="B91" s="111"/>
+      <c r="C91" s="55"/>
+      <c r="D91" s="55"/>
+      <c r="E91" s="55"/>
+      <c r="F91" s="55"/>
+      <c r="G91" s="55"/>
+      <c r="H91" s="308"/>
+      <c r="I91" s="309"/>
+      <c r="J91" s="109"/>
+      <c r="K91" s="112"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+    </row>
+    <row r="92" spans="1:13" ht="61.2">
       <c r="A92" s="4"/>
-    </row>
-    <row r="93" spans="1:13">
+      <c r="B92" s="113"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="308"/>
+      <c r="I92" s="309"/>
+      <c r="J92" s="109"/>
+      <c r="K92" s="112"/>
+      <c r="L92" s="114"/>
+      <c r="M92" s="115"/>
+    </row>
+    <row r="93" spans="1:13" ht="61.2">
       <c r="A93" s="4"/>
-    </row>
-    <row r="94" spans="1:13">
+      <c r="B93" s="113"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="308"/>
+      <c r="I93" s="309"/>
+      <c r="J93" s="109"/>
+      <c r="K93" s="112"/>
+      <c r="L93" s="114"/>
+      <c r="M93" s="115"/>
+    </row>
+    <row r="94" spans="1:13" ht="61.2">
       <c r="A94" s="4"/>
+      <c r="B94" s="113"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="308"/>
+      <c r="I94" s="309"/>
+      <c r="J94" s="109"/>
+      <c r="K94" s="112"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="4"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="4"/>
@@ -5494,83 +5810,102 @@
     <row r="111" spans="1:1">
       <c r="A111" s="4"/>
     </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="4"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4"/>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4"/>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4"/>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="4"/>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="4"/>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4"/>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="4"/>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="4"/>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="96">
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H84:I84"/>
+  <mergeCells count="103">
+    <mergeCell ref="H93:I93"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="H87:I87"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="H90:I90"/>
+    <mergeCell ref="H91:I91"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
     <mergeCell ref="H77:I77"/>
     <mergeCell ref="H78:I78"/>
     <mergeCell ref="H79:I79"/>
     <mergeCell ref="H80:I80"/>
-    <mergeCell ref="H81:I81"/>
     <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="C62:G62"/>
     <mergeCell ref="H62:I62"/>
     <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
     <mergeCell ref="H65:I65"/>
+    <mergeCell ref="C66:G66"/>
     <mergeCell ref="H66:I66"/>
     <mergeCell ref="H67:I67"/>
     <mergeCell ref="H68:I68"/>
     <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H49:I49"/>
     <mergeCell ref="H50:I50"/>
-    <mergeCell ref="C52:G52"/>
+    <mergeCell ref="H28:I28"/>
     <mergeCell ref="H52:I52"/>
     <mergeCell ref="H53:I53"/>
     <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="C56:G56"/>
     <mergeCell ref="H56:I56"/>
     <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H46:I46"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="F14:G15"/>
     <mergeCell ref="H14:I15"/>
     <mergeCell ref="J15:J16"/>
     <mergeCell ref="K15:K16"/>
     <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="H13:I13"/>
     <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:K2"/>
@@ -5584,18 +5919,36 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="C6:E6"/>
-    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="C48:G49"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="H34:I34"/>
-    <mergeCell ref="C38:G39"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="14" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="12" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>